--- a/Data/EXCEL/Transfer/bzPerformance/20250413PAP/4417-bzPerformance_perAndPbr20250413PAP.xlsx
+++ b/Data/EXCEL/Transfer/bzPerformance/20250413PAP/4417-bzPerformance_perAndPbr20250413PAP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20250413PAP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\20250413PAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AD4D04C-F56E-497A-951C-2C9F148761AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A183077-C4CD-42AE-8CAB-CF576F4F5AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{DB9DC71D-BDEC-4A6F-A5F3-4C6CEE82F725}"/>
+    <workbookView xWindow="1800" yWindow="840" windowWidth="17640" windowHeight="14310" xr2:uid="{00EB62DD-F211-4827-A61B-5B87D59DCB87}"/>
   </bookViews>
   <sheets>
     <sheet name="4417-bzPerformance_perAndPbr202" sheetId="2" r:id="rId1"/>
@@ -1261,21 +1261,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64DE7AC9-24A6-427A-9C9D-403D669F66C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6676EEDA-BF4C-47A7-B9E5-0AF1321D1302}">
   <dimension ref="A1:Q31"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="3" width="11.77734375" customWidth="1"/>
-    <col min="4" max="6" width="12.21875" customWidth="1"/>
-    <col min="7" max="9" width="11.77734375" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="13" width="11.77734375" customWidth="1"/>
-    <col min="14" max="14" width="12.21875" customWidth="1"/>
-    <col min="15" max="16" width="11.77734375" customWidth="1"/>
-    <col min="17" max="17" width="12.44140625" customWidth="1"/>
+    <col min="1" max="3" width="8.6328125" customWidth="1"/>
+    <col min="4" max="6" width="9.08984375" customWidth="1"/>
+    <col min="7" max="9" width="8.6328125" customWidth="1"/>
+    <col min="10" max="10" width="7.7265625" customWidth="1"/>
+    <col min="11" max="13" width="8.6328125" customWidth="1"/>
+    <col min="14" max="14" width="9.08984375" customWidth="1"/>
+    <col min="15" max="16" width="8.6328125" customWidth="1"/>
+    <col min="17" max="17" width="9.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1306,7 +1306,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A2" s="16"/>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -1357,7 +1357,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="17"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1394,7 +1394,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A4" s="6">
         <v>2025</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A5" s="10">
         <v>2024</v>
       </c>
@@ -1500,7 +1500,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>2023</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A7" s="10">
         <v>2022</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A8" s="6">
         <v>2021</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A9" s="10">
         <v>2020</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A10" s="6">
         <v>2019</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A11" s="10">
         <v>2018</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <v>2017</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A13" s="10">
         <v>2016</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A14" s="6">
         <v>2015</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A15" s="10">
         <v>2014</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A16" s="6">
         <v>2013</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A17" s="10">
         <v>2012</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A18" s="6">
         <v>2011</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A19" s="10">
         <v>2010</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A20" s="6">
         <v>2009</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A21" s="10">
         <v>2008</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A22" s="6">
         <v>2007</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A23" s="10">
         <v>2006</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A24" s="6">
         <v>2005</v>
       </c>
@@ -2507,7 +2507,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A25" s="10">
         <v>2004</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A26" s="6">
         <v>2003</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A27" s="10">
         <v>2002</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A28" s="6">
         <v>2001</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A29" s="10">
         <v>2000</v>
       </c>
@@ -2772,7 +2772,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A30" s="6">
         <v>1999</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A31" s="10">
         <v>1998</v>
       </c>
